--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5438-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5438-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{737A3217-6A65-4CC3-A877-26C8F461C541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F329291B-E9C1-4224-AAA0-96E3874BB992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{015AC8B0-50F3-4055-AEFD-C81492E0FF2F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{138953E8-B604-4D57-A0A8-1D54B9165244}"/>
   </bookViews>
   <sheets>
     <sheet name="5438-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1550,30 +1550,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9912D31D-2F68-434E-8455-1973C8931D1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6402CAB-9A27-49D5-AAC9-9BDFBA22D774}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1607,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1643,7 +1643,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1763,7 +1763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2023</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2022</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2021</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2019</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2018</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2017</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2016</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2015</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2014</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2013</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2012</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2011</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2010</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2009</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2008</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2007</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2006</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2005</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2004</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2003</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="43"/>
       <c r="B29" s="44"/>
       <c r="C29" s="20" t="s">
@@ -3521,7 +3521,7 @@
       <c r="W29" s="50"/>
       <c r="X29" s="46"/>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2002</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2001</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2000</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1999</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1998</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
         <v>59</v>
       </c>
